--- a/Body/parts_list.xlsx
+++ b/Body/parts_list.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29429"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{742041D8-421D-4C23-9BF7-336BDE4390BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3E8F83EC-5626-4A41-B78A-06027A6F3A5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -87,7 +87,7 @@
     <t>Total:</t>
   </si>
   <si>
-    <t>(Note: +3 is just for the body's possible price)</t>
+    <t>(Note: +50 is just for the body's and PSU/battery's possible price)</t>
   </si>
 </sst>
 </file>
@@ -616,11 +616,11 @@
         <v>17</v>
       </c>
       <c r="B7" s="7">
-        <f>B2*4+B3+B4+3</f>
-        <v>34.299999999999997</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="29.25">
+        <f>B2*4+B3+B4+50</f>
+        <v>81.3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="43.5">
       <c r="B8" s="6" t="s">
         <v>18</v>
       </c>
